--- a/public/templates/template-pm-request.xlsx
+++ b/public/templates/template-pm-request.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marth\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28AB329F-6627-4CD2-BA85-916BF956A06A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47746C16-EC98-45F0-8E6E-DD59CC97AB81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{206DC4D3-AD0A-4DF7-B945-16D682D170FD}"/>
   </bookViews>
@@ -46,9 +46,6 @@
     <t>Item</t>
   </si>
   <si>
-    <t>Unit</t>
-  </si>
-  <si>
     <t>Qty</t>
   </si>
   <si>
@@ -89,6 +86,9 @@
   </si>
   <si>
     <t>Price</t>
+  </si>
+  <si>
+    <t>Uom</t>
   </si>
 </sst>
 </file>
@@ -504,7 +504,7 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -515,22 +515,22 @@
         <v>2</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D3" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="E3" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="F3" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="F3" s="6" t="s">
-        <v>5</v>
-      </c>
       <c r="G3" s="5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H3" s="8" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
@@ -538,13 +538,13 @@
         <v>1</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E4" s="3">
         <v>2</v>
@@ -553,7 +553,7 @@
         <v>45912</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H4" s="9">
         <v>200000</v>
@@ -564,13 +564,13 @@
         <v>2</v>
       </c>
       <c r="B5" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="D5" s="3" t="s">
         <v>15</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>16</v>
       </c>
       <c r="E5" s="3">
         <v>50</v>
@@ -579,7 +579,7 @@
         <v>45789</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H5" s="9">
         <v>78600</v>
@@ -590,13 +590,13 @@
         <v>3</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E6" s="3">
         <v>2</v>
@@ -605,7 +605,7 @@
         <v>45912</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H6" s="9">
         <v>425000</v>
@@ -616,13 +616,13 @@
         <v>4</v>
       </c>
       <c r="B7" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C7" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="D7" s="3" t="s">
         <v>15</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>16</v>
       </c>
       <c r="E7" s="3">
         <v>50</v>
@@ -631,7 +631,7 @@
         <v>45789</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H7" s="9">
         <v>21000</v>
@@ -1096,17 +1096,17 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/public/templates/template-pm-request.xlsx
+++ b/public/templates/template-pm-request.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marth\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47746C16-EC98-45F0-8E6E-DD59CC97AB81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E055A9D-77C5-41EE-9537-76FAABB2F7E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{206DC4D3-AD0A-4DF7-B945-16D682D170FD}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="17">
   <si>
     <t>Project:</t>
   </si>
@@ -83,9 +83,6 @@
   </si>
   <si>
     <t>kg</t>
-  </si>
-  <si>
-    <t>Price</t>
   </si>
   <si>
     <t>Uom</t>
@@ -95,8 +92,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
-    <numFmt numFmtId="44" formatCode="_-&quot;Rp&quot;* #,##0.00_-;\-&quot;Rp&quot;* #,##0.00_-;_-&quot;Rp&quot;* &quot;-&quot;??_-;_-@_-"/>
+  <numFmts count="1">
     <numFmt numFmtId="164" formatCode="[$-13809]dddd\,\ dd\ mmmm\ yyyy;@"/>
   </numFmts>
   <fonts count="1" x14ac:knownFonts="1">
@@ -149,7 +145,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -167,11 +163,6 @@
     <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="44" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -486,7 +477,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{55677A52-26E2-48EC-AB6E-279B4639D49C}">
-  <dimension ref="A1:H50"/>
+  <dimension ref="A1:G50"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="7.44140625" customWidth="1"/>
@@ -496,10 +487,9 @@
     <col min="5" max="5" width="11.6640625" customWidth="1"/>
     <col min="6" max="6" width="22.21875" style="2" customWidth="1"/>
     <col min="7" max="7" width="16.6640625" customWidth="1"/>
-    <col min="8" max="8" width="18.33203125" style="7" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -507,7 +497,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
         <v>1</v>
       </c>
@@ -518,7 +508,7 @@
         <v>5</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E3" s="5" t="s">
         <v>3</v>
@@ -529,11 +519,8 @@
       <c r="G3" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="H3" s="8" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="3">
         <v>1</v>
       </c>
@@ -555,11 +542,8 @@
       <c r="G4" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H4" s="9">
-        <v>200000</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="3">
         <v>2</v>
       </c>
@@ -581,11 +565,8 @@
       <c r="G5" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H5" s="9">
-        <v>78600</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="3">
         <v>3</v>
       </c>
@@ -607,11 +588,8 @@
       <c r="G6" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H6" s="9">
-        <v>425000</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="3">
         <v>4</v>
       </c>
@@ -633,11 +611,8 @@
       <c r="G7" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H7" s="9">
-        <v>21000</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="3"/>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
@@ -645,9 +620,8 @@
       <c r="E8" s="3"/>
       <c r="F8" s="4"/>
       <c r="G8" s="3"/>
-      <c r="H8" s="9"/>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="3"/>
       <c r="B9" s="3"/>
       <c r="C9" s="3"/>
@@ -655,9 +629,8 @@
       <c r="E9" s="3"/>
       <c r="F9" s="4"/>
       <c r="G9" s="3"/>
-      <c r="H9" s="9"/>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="3"/>
       <c r="B10" s="3"/>
       <c r="C10" s="3"/>
@@ -665,9 +638,8 @@
       <c r="E10" s="3"/>
       <c r="F10" s="4"/>
       <c r="G10" s="3"/>
-      <c r="H10" s="9"/>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="3"/>
       <c r="B11" s="3"/>
       <c r="C11" s="3"/>
@@ -675,9 +647,8 @@
       <c r="E11" s="3"/>
       <c r="F11" s="4"/>
       <c r="G11" s="3"/>
-      <c r="H11" s="9"/>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="3"/>
       <c r="B12" s="3"/>
       <c r="C12" s="3"/>
@@ -685,9 +656,8 @@
       <c r="E12" s="3"/>
       <c r="F12" s="4"/>
       <c r="G12" s="3"/>
-      <c r="H12" s="9"/>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="3"/>
       <c r="B13" s="3"/>
       <c r="C13" s="3"/>
@@ -695,9 +665,8 @@
       <c r="E13" s="3"/>
       <c r="F13" s="4"/>
       <c r="G13" s="3"/>
-      <c r="H13" s="9"/>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="3"/>
       <c r="B14" s="3"/>
       <c r="C14" s="3"/>
@@ -705,9 +674,8 @@
       <c r="E14" s="3"/>
       <c r="F14" s="4"/>
       <c r="G14" s="3"/>
-      <c r="H14" s="9"/>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" s="3"/>
       <c r="B15" s="3"/>
       <c r="C15" s="3"/>
@@ -715,9 +683,8 @@
       <c r="E15" s="3"/>
       <c r="F15" s="4"/>
       <c r="G15" s="3"/>
-      <c r="H15" s="9"/>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="3"/>
       <c r="B16" s="3"/>
       <c r="C16" s="3"/>
@@ -725,9 +692,8 @@
       <c r="E16" s="3"/>
       <c r="F16" s="4"/>
       <c r="G16" s="3"/>
-      <c r="H16" s="9"/>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" s="3"/>
       <c r="B17" s="3"/>
       <c r="C17" s="3"/>
@@ -735,9 +701,8 @@
       <c r="E17" s="3"/>
       <c r="F17" s="4"/>
       <c r="G17" s="3"/>
-      <c r="H17" s="9"/>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" s="3"/>
       <c r="B18" s="3"/>
       <c r="C18" s="3"/>
@@ -745,9 +710,8 @@
       <c r="E18" s="3"/>
       <c r="F18" s="4"/>
       <c r="G18" s="3"/>
-      <c r="H18" s="9"/>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" s="3"/>
       <c r="B19" s="3"/>
       <c r="C19" s="3"/>
@@ -755,9 +719,8 @@
       <c r="E19" s="3"/>
       <c r="F19" s="4"/>
       <c r="G19" s="3"/>
-      <c r="H19" s="9"/>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" s="3"/>
       <c r="B20" s="3"/>
       <c r="C20" s="3"/>
@@ -765,9 +728,8 @@
       <c r="E20" s="3"/>
       <c r="F20" s="4"/>
       <c r="G20" s="3"/>
-      <c r="H20" s="9"/>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" s="3"/>
       <c r="B21" s="3"/>
       <c r="C21" s="3"/>
@@ -775,9 +737,8 @@
       <c r="E21" s="3"/>
       <c r="F21" s="4"/>
       <c r="G21" s="3"/>
-      <c r="H21" s="9"/>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" s="3"/>
       <c r="B22" s="3"/>
       <c r="C22" s="3"/>
@@ -785,9 +746,8 @@
       <c r="E22" s="3"/>
       <c r="F22" s="4"/>
       <c r="G22" s="3"/>
-      <c r="H22" s="9"/>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" s="3"/>
       <c r="B23" s="3"/>
       <c r="C23" s="3"/>
@@ -795,9 +755,8 @@
       <c r="E23" s="3"/>
       <c r="F23" s="4"/>
       <c r="G23" s="3"/>
-      <c r="H23" s="9"/>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" s="3"/>
       <c r="B24" s="3"/>
       <c r="C24" s="3"/>
@@ -805,9 +764,8 @@
       <c r="E24" s="3"/>
       <c r="F24" s="4"/>
       <c r="G24" s="3"/>
-      <c r="H24" s="9"/>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" s="3"/>
       <c r="B25" s="3"/>
       <c r="C25" s="3"/>
@@ -815,9 +773,8 @@
       <c r="E25" s="3"/>
       <c r="F25" s="4"/>
       <c r="G25" s="3"/>
-      <c r="H25" s="9"/>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" s="3"/>
       <c r="B26" s="3"/>
       <c r="C26" s="3"/>
@@ -825,9 +782,8 @@
       <c r="E26" s="3"/>
       <c r="F26" s="4"/>
       <c r="G26" s="3"/>
-      <c r="H26" s="9"/>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" s="3"/>
       <c r="B27" s="3"/>
       <c r="C27" s="3"/>
@@ -835,9 +791,8 @@
       <c r="E27" s="3"/>
       <c r="F27" s="4"/>
       <c r="G27" s="3"/>
-      <c r="H27" s="9"/>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" s="3"/>
       <c r="B28" s="3"/>
       <c r="C28" s="3"/>
@@ -845,9 +800,8 @@
       <c r="E28" s="3"/>
       <c r="F28" s="4"/>
       <c r="G28" s="3"/>
-      <c r="H28" s="9"/>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" s="3"/>
       <c r="B29" s="3"/>
       <c r="C29" s="3"/>
@@ -855,9 +809,8 @@
       <c r="E29" s="3"/>
       <c r="F29" s="4"/>
       <c r="G29" s="3"/>
-      <c r="H29" s="9"/>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" s="3"/>
       <c r="B30" s="3"/>
       <c r="C30" s="3"/>
@@ -865,9 +818,8 @@
       <c r="E30" s="3"/>
       <c r="F30" s="4"/>
       <c r="G30" s="3"/>
-      <c r="H30" s="9"/>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" s="3"/>
       <c r="B31" s="3"/>
       <c r="C31" s="3"/>
@@ -875,9 +827,8 @@
       <c r="E31" s="3"/>
       <c r="F31" s="4"/>
       <c r="G31" s="3"/>
-      <c r="H31" s="9"/>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" s="3"/>
       <c r="B32" s="3"/>
       <c r="C32" s="3"/>
@@ -885,9 +836,8 @@
       <c r="E32" s="3"/>
       <c r="F32" s="4"/>
       <c r="G32" s="3"/>
-      <c r="H32" s="9"/>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33" s="3"/>
       <c r="B33" s="3"/>
       <c r="C33" s="3"/>
@@ -895,9 +845,8 @@
       <c r="E33" s="3"/>
       <c r="F33" s="4"/>
       <c r="G33" s="3"/>
-      <c r="H33" s="9"/>
-    </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34" s="3"/>
       <c r="B34" s="3"/>
       <c r="C34" s="3"/>
@@ -905,9 +854,8 @@
       <c r="E34" s="3"/>
       <c r="F34" s="4"/>
       <c r="G34" s="3"/>
-      <c r="H34" s="9"/>
-    </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35" s="3"/>
       <c r="B35" s="3"/>
       <c r="C35" s="3"/>
@@ -915,9 +863,8 @@
       <c r="E35" s="3"/>
       <c r="F35" s="4"/>
       <c r="G35" s="3"/>
-      <c r="H35" s="9"/>
-    </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36" s="3"/>
       <c r="B36" s="3"/>
       <c r="C36" s="3"/>
@@ -925,9 +872,8 @@
       <c r="E36" s="3"/>
       <c r="F36" s="4"/>
       <c r="G36" s="3"/>
-      <c r="H36" s="9"/>
-    </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37" s="3"/>
       <c r="B37" s="3"/>
       <c r="C37" s="3"/>
@@ -935,9 +881,8 @@
       <c r="E37" s="3"/>
       <c r="F37" s="4"/>
       <c r="G37" s="3"/>
-      <c r="H37" s="9"/>
-    </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38" s="3"/>
       <c r="B38" s="3"/>
       <c r="C38" s="3"/>
@@ -945,9 +890,8 @@
       <c r="E38" s="3"/>
       <c r="F38" s="4"/>
       <c r="G38" s="3"/>
-      <c r="H38" s="9"/>
-    </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39" s="3"/>
       <c r="B39" s="3"/>
       <c r="C39" s="3"/>
@@ -955,9 +899,8 @@
       <c r="E39" s="3"/>
       <c r="F39" s="4"/>
       <c r="G39" s="3"/>
-      <c r="H39" s="9"/>
-    </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40" s="3"/>
       <c r="B40" s="3"/>
       <c r="C40" s="3"/>
@@ -965,9 +908,8 @@
       <c r="E40" s="3"/>
       <c r="F40" s="4"/>
       <c r="G40" s="3"/>
-      <c r="H40" s="9"/>
-    </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41" s="3"/>
       <c r="B41" s="3"/>
       <c r="C41" s="3"/>
@@ -975,9 +917,8 @@
       <c r="E41" s="3"/>
       <c r="F41" s="4"/>
       <c r="G41" s="3"/>
-      <c r="H41" s="9"/>
-    </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42" s="3"/>
       <c r="B42" s="3"/>
       <c r="C42" s="3"/>
@@ -985,9 +926,8 @@
       <c r="E42" s="3"/>
       <c r="F42" s="4"/>
       <c r="G42" s="3"/>
-      <c r="H42" s="9"/>
-    </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43" s="3"/>
       <c r="B43" s="3"/>
       <c r="C43" s="3"/>
@@ -995,9 +935,8 @@
       <c r="E43" s="3"/>
       <c r="F43" s="4"/>
       <c r="G43" s="3"/>
-      <c r="H43" s="9"/>
-    </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44" s="3"/>
       <c r="B44" s="3"/>
       <c r="C44" s="3"/>
@@ -1005,9 +944,8 @@
       <c r="E44" s="3"/>
       <c r="F44" s="4"/>
       <c r="G44" s="3"/>
-      <c r="H44" s="9"/>
-    </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45" s="3"/>
       <c r="B45" s="3"/>
       <c r="C45" s="3"/>
@@ -1015,9 +953,8 @@
       <c r="E45" s="3"/>
       <c r="F45" s="4"/>
       <c r="G45" s="3"/>
-      <c r="H45" s="9"/>
-    </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A46" s="3"/>
       <c r="B46" s="3"/>
       <c r="C46" s="3"/>
@@ -1025,9 +962,8 @@
       <c r="E46" s="3"/>
       <c r="F46" s="4"/>
       <c r="G46" s="3"/>
-      <c r="H46" s="9"/>
-    </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47" s="3"/>
       <c r="B47" s="3"/>
       <c r="C47" s="3"/>
@@ -1035,9 +971,8 @@
       <c r="E47" s="3"/>
       <c r="F47" s="4"/>
       <c r="G47" s="3"/>
-      <c r="H47" s="9"/>
-    </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48" s="3"/>
       <c r="B48" s="3"/>
       <c r="C48" s="3"/>
@@ -1045,9 +980,8 @@
       <c r="E48" s="3"/>
       <c r="F48" s="4"/>
       <c r="G48" s="3"/>
-      <c r="H48" s="9"/>
-    </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.3">
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A49" s="3"/>
       <c r="B49" s="3"/>
       <c r="C49" s="3"/>
@@ -1055,9 +989,8 @@
       <c r="E49" s="3"/>
       <c r="F49" s="4"/>
       <c r="G49" s="3"/>
-      <c r="H49" s="9"/>
-    </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A50" s="3"/>
       <c r="B50" s="3"/>
       <c r="C50" s="3"/>
@@ -1065,7 +998,6 @@
       <c r="E50" s="3"/>
       <c r="F50" s="4"/>
       <c r="G50" s="3"/>
-      <c r="H50" s="9"/>
     </row>
   </sheetData>
   <dataValidations count="1">
